--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T04:00:55+00:00</t>
+    <t>2026-09-02T06:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="59">
   <si>
     <t>Property</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,12 +121,30 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>HP:0011460</t>
+  </si>
+  <si>
+    <t>Embryonal onset</t>
+  </si>
+  <si>
+    <t>HP:0011461</t>
+  </si>
+  <si>
+    <t>Fetal onset</t>
+  </si>
+  <si>
     <t>HP:0003577</t>
   </si>
   <si>
     <t>Congenital onset</t>
   </si>
   <si>
+    <t>HP:0003623</t>
+  </si>
+  <si>
+    <t>Neonatal onset</t>
+  </si>
+  <si>
     <t>HP:0003593</t>
   </si>
   <si>
@@ -145,46 +163,34 @@
     <t>Juvenile onset</t>
   </si>
   <si>
+    <t>HP:0011462</t>
+  </si>
+  <si>
+    <t>Young adult onset</t>
+  </si>
+  <si>
+    <t>HP:0025708</t>
+  </si>
+  <si>
+    <t>Early young adult onset</t>
+  </si>
+  <si>
     <t>HP:0003581</t>
   </si>
   <si>
     <t>Adult onset</t>
   </si>
   <si>
+    <t>HP:0003596</t>
+  </si>
+  <si>
+    <t>Middle age onset</t>
+  </si>
+  <si>
     <t>HP:0003584</t>
   </si>
   <si>
     <t>Late onset</t>
-  </si>
-  <si>
-    <t>HP:0011462</t>
-  </si>
-  <si>
-    <t>Young adult onset</t>
-  </si>
-  <si>
-    <t>HP:0025708</t>
-  </si>
-  <si>
-    <t>Middle age onset</t>
-  </si>
-  <si>
-    <t>HP:0003596</t>
-  </si>
-  <si>
-    <t>Neonatal onset</t>
-  </si>
-  <si>
-    <t>HP:0034198</t>
-  </si>
-  <si>
-    <t>Fetal onset</t>
-  </si>
-  <si>
-    <t>HP:0034199</t>
-  </si>
-  <si>
-    <t>Embryonal onset</t>
   </si>
 </sst>
 </file>
@@ -498,7 +504,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -603,17 +609,25 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>31</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B14" t="s" s="2">
+      <c r="B15" t="s" s="2">
         <v>33</v>
       </c>
     </row>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -37,7 +37,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>HPOAgeOfOnsetValueSet</t>
+    <t>MII_VS_Seltene_HPOAgeOfOnset</t>
   </si>
   <si>
     <t>Title</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-hpo-age-of-onset.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
